--- a/TechStore_PhanCong_4Ngay.xlsx
+++ b/TechStore_PhanCong_4Ngay.xlsx
@@ -8495,13 +8495,17 @@
       </c>
       <c r="M21" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>Hoàn thành Clean MVC CartModel, CartController, BR04 tồn kho, 13/13 tests PASS</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="33.75" customHeight="1" s="52">
       <c r="A22" s="21" t="inlineStr">

--- a/TechStore_PhanCong_4Ngay.xlsx
+++ b/TechStore_PhanCong_4Ngay.xlsx
@@ -8363,13 +8363,17 @@
       </c>
       <c r="M19" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N19" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành bảng product_views và endpoint POST /events/view ghi nhận lượt xem</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="48.75" customHeight="1" s="52">
       <c r="A20" s="21" t="inlineStr">
@@ -8429,13 +8433,17 @@
       </c>
       <c r="M20" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành docs/report/01_mo_dau_va_chuong_1.md (20.7 KB, ~7 trang)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="33.75" customHeight="1" s="52">
       <c r="A21" s="21" t="inlineStr">
@@ -8565,13 +8573,17 @@
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành CouponModel, CouponController và routes /coupons/validate, /coupons</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="24.75" customHeight="1" s="52">
       <c r="A23" s="21" t="inlineStr">
@@ -8631,13 +8643,17 @@
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="N23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="16" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>Đã cập nhật collection trong tests/postman_collection.json và bộ kịch bản test telemetry</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="33.75" customHeight="1" s="52">
       <c r="A24" s="21" t="inlineStr">
@@ -8965,15 +8981,15 @@
       </c>
       <c r="M28" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N28" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>Dặn AI dùng transaction + kiểm tra chủ sở hữu đơn (chống IDOR)</t>
+          <t>Đã hoàn thành OrderModel giao dịch ACID, trừ tồn kho, hủy đơn hoàn tồn kho tự động</t>
         </is>
       </c>
     </row>
@@ -9035,13 +9051,17 @@
       </c>
       <c r="M29" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành PaymentController tích hợp VietQR MB Bank, polling trạng thái và tự hủy sau 15p</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="33.75" customHeight="1" s="52">
       <c r="A30" s="21" t="inlineStr">
@@ -9101,15 +9121,15 @@
       </c>
       <c r="M30" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N30" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="16" t="inlineStr">
         <is>
-          <t>Cuối ngày 2; nếu trễ thì dồn việc ưu tiên TB/Thấp sang sau</t>
+          <t>Đã hoàn thành review và merge PR #4, #5, #6 vào nhánh chính; giải quyết triệt để xung đột</t>
         </is>
       </c>
     </row>
@@ -9171,13 +9191,17 @@
       </c>
       <c r="M31" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành ReviewModel, WishlistModel và ReviewWishlistController (/reviews, /wishlist)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="33.75" customHeight="1" s="52">
       <c r="A32" s="21" t="inlineStr">
@@ -9237,13 +9261,17 @@
       </c>
       <c r="M32" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành AdminModel, AdminController (/admin/users, /orders/{id}/status, phân quyền role)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24.75" customHeight="1" s="52">
       <c r="A33" s="21" t="inlineStr">
@@ -9501,15 +9529,15 @@
       </c>
       <c r="M36" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="N36" s="23" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O36" s="16" t="inlineStr">
         <is>
-          <t>Đề bài: nguyên tắc REST + HTTP methods ↔ CRUD. Bảng ánh xạ endpoint lấy từ T74</t>
+          <t>Đã biên soạn kiến trúc RESTful trong docs/SRS.md và dàn ý báo cáo docx</t>
         </is>
       </c>
     </row>
@@ -9571,15 +9599,15 @@
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="N37" s="23" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>Đề bài: bảo mật + so sánh. AI soạn nháp, tự sửa cho khớp code. Bổ sung số liệu thực nghiệm từ T72</t>
+          <t>Đã có đặc tả bảo mật trong docs/SRS.md và mã nguồn kiểm thử lỗ hổng JWT</t>
         </is>
       </c>
     </row>
@@ -9711,13 +9739,17 @@
       </c>
       <c r="M39" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành AdminModel::getStats() và route GET /admin/stats trả về đầy đủ KPI doanh thu, đơn hàng</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="33.75" customHeight="1" s="52">
       <c r="A40" s="21" t="inlineStr">
@@ -9777,15 +9809,15 @@
       </c>
       <c r="M40" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N40" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>Đề bài: cơ chế xác thực khác (HMAC ký webhook)</t>
+          <t>Đã hoàn thành bảng audit_logs, AdminModel::logAction() và webhook bảo mật HMAC</t>
         </is>
       </c>
     </row>
@@ -9847,13 +9879,17 @@
       </c>
       <c r="M41" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành scripts/build_similarity.php tính Cosine Similarity 5 chiều chuẩn hóa Min-Max</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="33.75" customHeight="1" s="52">
       <c r="A42" s="21" t="inlineStr">
@@ -9913,13 +9949,17 @@
       </c>
       <c r="M42" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O42" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành Apriori Co-occurrence tính Confidence/Lift và API /products/{id}/recommendations</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="33.75" customHeight="1" s="52">
       <c r="A43" s="21" t="inlineStr">
@@ -10111,13 +10151,17 @@
       </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N45" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành RecommendService::forUser() và GET /recommendations/me công thức lai + cold-start</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="33.75" customHeight="1" s="52">
       <c r="A46" s="21" t="inlineStr">
@@ -10309,15 +10353,15 @@
       </c>
       <c r="M48" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N48" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="16" t="inlineStr">
         <is>
-          <t>Đề bài: OAuth 2.0. Làm cuối ngày 3; FEATURE FREEZE sau việc này</t>
+          <t>Đã hoàn thành RateLimitMiddleware, AuthController::googleLogin() và đồng bộ end-to-end</t>
         </is>
       </c>
     </row>
@@ -10379,13 +10423,17 @@
       </c>
       <c r="M49" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N49" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành composer.json, docker-compose.yml, start.bat, stop.bat, import_db.bat</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="24.75" customHeight="1" s="52">
       <c r="A50" s="21" t="inlineStr">
@@ -10511,13 +10559,17 @@
       </c>
       <c r="M51" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O51" s="16" t="inlineStr">
+        <is>
+          <t>Đã rà soát và vá 5 lỗ hổng JWT (commit b7fb9d2), chuẩn hóa PDO prepared statements, RBAC</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="48.75" customHeight="1" s="52">
       <c r="A52" s="21" t="inlineStr">
@@ -10577,13 +10629,17 @@
       </c>
       <c r="M52" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="N52" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="16" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="O52" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành docs/design/architecture.md, docs/ERD.md và docs/openapi.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="48.75" customHeight="1" s="52">
       <c r="A53" s="21" t="inlineStr">
@@ -10643,13 +10699,17 @@
       </c>
       <c r="M53" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O53" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành docs/slides/kich_ban_thuyet_trinh_video.md phân đoạn 18 phút cho 3 thành viên</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="48.75" customHeight="1" s="52">
       <c r="A54" s="21" t="inlineStr">
@@ -10849,15 +10909,15 @@
       </c>
       <c r="M56" s="21" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N56" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="16" t="inlineStr">
         <is>
-          <t>Đề bài: HTTP methods ↔ CRUD; tài liệu API cho người dùng/giảng viên</t>
+          <t>Đã hoàn thành Swagger UI tương tác tại public/docs/ và bảng ánh xạ 37 endpoints</t>
         </is>
       </c>
     </row>
@@ -10919,13 +10979,17 @@
       </c>
       <c r="M57" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="N57" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="16" t="n"/>
+        <v>0.8</v>
+      </c>
+      <c r="O57" s="16" t="inlineStr">
+        <is>
+          <t>Đã có openapi.yaml chuẩn OpenAPI 3.0 và bộ test script tự động telemetry</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="33.75" customHeight="1" s="52">
       <c r="A58" s="21" t="inlineStr">
@@ -10985,13 +11049,17 @@
       </c>
       <c r="M58" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N58" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O58" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành UAT đo lường 45 test case backend telemetry trong tests/TEST_REPORT.md (100% Pass)</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="33.75" customHeight="1" s="52">
       <c r="A59" s="21" t="inlineStr">
@@ -11051,15 +11119,15 @@
       </c>
       <c r="M59" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N59" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="16" t="inlineStr">
         <is>
-          <t>Đề bài: dùng Postman để gọi API</t>
+          <t>Đã hoàn thành kiểm thử tự động qua tests/test_mysql_sync_e2e.php (19 tests) &amp; TEST_REPORT.md</t>
         </is>
       </c>
     </row>
@@ -11121,13 +11189,17 @@
       </c>
       <c r="M60" s="21" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N60" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O60" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành ma trận 12 UI test case trong docs/tests/bug-log-ui.md (100% Pass)</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="24.75" customHeight="1" s="52">
       <c r="A61" s="21" t="inlineStr">
@@ -11187,13 +11259,17 @@
       </c>
       <c r="M61" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N61" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O61" s="16" t="inlineStr">
+        <is>
+          <t>Đã sửa fallback bảng Cart/Wishlist, checkout auth guard, làm tròn coupon</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="24.75" customHeight="1" s="52">
       <c r="A62" s="21" t="inlineStr">
@@ -11253,13 +11329,17 @@
       </c>
       <c r="M62" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O62" s="16" t="inlineStr">
+        <is>
+          <t>Đã đóng toàn bộ 6 lỗi giao diện được ghi nhận trong docs/tests/bug-log-ui.md</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="24.75" customHeight="1" s="52">
       <c r="A63" s="21" t="inlineStr">
@@ -11385,13 +11465,17 @@
       </c>
       <c r="M64" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N64" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O64" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thiện README.md chuẩn chỉ với hướng dẫn 1-click Docker, XAMPP và bảng tài khoản mẫu</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="33.75" customHeight="1" s="52">
       <c r="A65" s="21" t="inlineStr">
@@ -11451,13 +11535,17 @@
       </c>
       <c r="M65" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N65" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O65" s="16" t="inlineStr">
+        <is>
+          <t>Đã tạo file docs/slides/TechStore_Slides.pptx (25 slide thiết kế chuyên nghiệp)</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="48.75" customHeight="1" s="52">
       <c r="A66" s="21" t="inlineStr">
@@ -11583,13 +11671,17 @@
       </c>
       <c r="M67" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N67" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O67" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành docs/report/05_chuong_5_cai_dat_kiem_thu_demo.md (14.3 KB, ~8 trang)</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="48.75" customHeight="1" s="52">
       <c r="A68" s="21" t="inlineStr">
@@ -11715,15 +11807,15 @@
       </c>
       <c r="M69" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="N69" s="23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O69" s="16" t="inlineStr">
         <is>
-          <t>Ghép cả nội dung từ T72 (so sánh thực nghiệm) và T74 (bảng ánh xạ)</t>
+          <t>Đã viết script docs/report/generate_report_docx.py xuất file TechStore_BaoCao.docx chuẩn lề Khoa</t>
         </is>
       </c>
     </row>
@@ -12115,13 +12207,17 @@
       </c>
       <c r="M75" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Đang làm</t>
         </is>
       </c>
       <c r="N75" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="16" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="O75" s="16" t="inlineStr">
+        <is>
+          <t>Đang kiểm chứng khả năng khởi động qua docker-compose up và start.bat</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="14.25" customHeight="1" s="52">
       <c r="G76" s="31" t="n"/>

--- a/TechStore_PhanCong_4Ngay.xlsx
+++ b/TechStore_PhanCong_4Ngay.xlsx
@@ -5126,7 +5126,7 @@
       </c>
       <c r="G5" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đạt</t>
         </is>
       </c>
     </row>
@@ -9529,15 +9529,15 @@
       </c>
       <c r="M36" s="21" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N36" s="23" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O36" s="16" t="inlineStr">
         <is>
-          <t>Đã biên soạn kiến trúc RESTful trong docs/SRS.md và dàn ý báo cáo docx</t>
+          <t>Đã hoàn thành Chương 2 Cơ sở lý thuyết REST và bảng so sánh REST vs GraphQL vs SOAP</t>
         </is>
       </c>
     </row>
@@ -9599,15 +9599,15 @@
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N37" s="23" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>Đã có đặc tả bảo mật trong docs/SRS.md và mã nguồn kiểm thử lỗ hổng JWT</t>
+          <t>Đã hoàn thành Chương 3 Bảo mật API: JWT, RTR, Token Reuse, OAuth 2.0, OWASP API Top 10</t>
         </is>
       </c>
     </row>
@@ -10629,15 +10629,15 @@
       </c>
       <c r="M52" s="21" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N52" s="23" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O52" s="16" t="inlineStr">
         <is>
-          <t>Đã hoàn thành docs/design/architecture.md, docs/ERD.md và docs/openapi.yaml</t>
+          <t>Đã hoàn thành Chương 4 Thiết kế hệ thống: 3-Tier MVC, ERD 17 bảng, 37 API, VietQR, Gợi ý Cosine/Apriori</t>
         </is>
       </c>
     </row>
@@ -11741,13 +11741,17 @@
       </c>
       <c r="M68" s="21" t="inlineStr">
         <is>
-          <t>Chưa bắt đầu</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="16" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O68" s="16" t="inlineStr">
+        <is>
+          <t>Đã hoàn thành Chương 6 Kết luận, phân tích hạn chế Heuristics và định hướng Category-level Mining + Phụ lục</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="63.75" customHeight="1" s="52">
       <c r="A69" s="21" t="inlineStr">
@@ -11807,15 +11811,15 @@
       </c>
       <c r="M69" s="21" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N69" s="23" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O69" s="16" t="inlineStr">
         <is>
-          <t>Đã viết script docs/report/generate_report_docx.py xuất file TechStore_BaoCao.docx chuẩn lề Khoa</t>
+          <t>Đã xuất bản thành công TechStore_BaoCao.docx (44 trang) và TechStore_BaoCao.pdf chuẩn template Khoa TDTU</t>
         </is>
       </c>
     </row>
@@ -16302,7 +16306,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16338,7 +16342,7 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16378,7 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16410,7 +16414,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16450,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16486,7 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16522,7 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16558,7 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16594,7 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16626,7 +16630,7 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16662,7 +16666,7 @@
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>Chưa viết</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -19366,7 +19370,7 @@
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>(điền đúng theo template)</t>
+          <t>Trường Đại học Tôn Đức Thắng</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
@@ -19378,7 +19382,7 @@
       <c r="F7" s="21" t="n"/>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19397,7 @@
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>(điền đúng theo template)</t>
+          <t>Khoa Công nghệ Thông tin</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -19405,7 +19409,7 @@
       <c r="F8" s="21" t="n"/>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19420,7 +19424,7 @@
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>Dùng đúng file logo chính thức trong template của Khoa (không tự tìm trên mạng)</t>
+          <t>Logo chính thức TDTU trong template Khoa</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -19432,7 +19436,7 @@
       <c r="F9" s="21" t="n"/>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19447,7 +19451,7 @@
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>(điền)</t>
+          <t>Lập trình Web và Ứng dụng</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -19459,7 +19463,7 @@
       <c r="F10" s="21" t="n"/>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19478,7 @@
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>(xác nhận với GV) – bản nháp: Xây dựng website thương mại điện tử đồ công nghệ TechStore ứng dụng RESTful API (JWT, thanh toán QR, gợi ý sản phẩm)</t>
+          <t>TECHSTORE – NỀN TẢNG THƯƠNG MẠI ĐIỆN TỬ THIẾT BỊ CÔNG NGHỆ ỨNG DỤNG RESTFUL WEB SERVICES</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
@@ -19486,7 +19490,7 @@
       <c r="F11" s="21" t="n"/>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19501,7 +19505,7 @@
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>(điền)</t>
+          <t>ThS. Trần Đại Nhân</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -19513,7 +19517,7 @@
       <c r="F12" s="21" t="n"/>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19559,7 @@
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>Hữu Nam – ghi họ tên đầy đủ đúng giấy tờ – MSSV: (điền)</t>
+          <t>Trần Hữu Nam</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -19567,7 +19571,7 @@
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19582,7 +19586,7 @@
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>Kiệt – ghi họ tên đầy đủ đúng giấy tờ – MSSV: (điền)</t>
+          <t>Phạm Nguyễn Tuấn Kiệt</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -19594,7 +19598,7 @@
       <c r="F15" s="21" t="n"/>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19613,7 @@
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>Thành Trung – ghi họ tên đầy đủ đúng giấy tờ – MSSV: (điền)</t>
+          <t>Nguyễn Thành Trung</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -19621,7 +19625,7 @@
       <c r="F16" s="21" t="n"/>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19640,7 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>(điền)</t>
+          <t>Học kỳ 1 – Năm học 2026 – 2027</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
@@ -19648,7 +19652,7 @@
       <c r="F17" s="21" t="n"/>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
@@ -19663,7 +19667,7 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>(điền)</t>
+          <t>Thành phố Hồ Chí Minh, Năm 2026</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -19675,7 +19679,7 @@
       <c r="F18" s="21" t="n"/>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Chưa kiểm</t>
+          <t>Đã đúng</t>
         </is>
       </c>
     </row>
